--- a/Leads.xlsx
+++ b/Leads.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,6 +638,972 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rittenhouse Square Chiropractic</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>http://rittenhousechiro.com/</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>frontdesk@rittenhousechiro.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>215) 546-1010, 215) 546-1010, 215-546-1010</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:09:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Advanced Chiropractic of Philadelphia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>http://www.phillychiro.com/</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>phillychiroadvanced@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>215)-800-7287, 215-800-7287, 215) 545-5117</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:09:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Brewerytown Chiropractic</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>http://www.brewerytownchiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>contact@brewerytownchiropractic.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>215-608-8191</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:09:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pain Free Chiropractic</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.phillypainfreechiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>kpainfreechiro@gmail.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>267-343-4930</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:09:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Movement Medicine Chiropractic Performance &amp; Recovery</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>http://www.movementmedicinerx.com/</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>info@movementmedicinerx.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>215)501-7760</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Great Life Chiropractic &amp; Massage</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://greatlifechiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>greatlife19128@gmail.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>215-483-6550, 19128 215-483</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:10:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Allegheny Family Chiropractic Center</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>http://spine-disc.com/</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>allegheny2514@gmail.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>215-425-1110</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:10:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Goodman Family Chiropractic</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://drgoodbones.com/</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>info@drgoodbones.com, drdave@drgoodbones.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>+1 215-725-3979, 215-725-3979, 215-323-4855</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:10:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Avon Chiropractic and Injury Center</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.avonchiropracticpa.com/</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>avonchiro2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>215) 613-5929</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:11:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mt. Airy Chiropractic</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>http://www.mtairychiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>info@mtairychiropractic.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>267) 309-9029, 267.309.9029</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:12:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Barry A. Wahner, DC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>http://www.drwahner.com/</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>wahnerchiro@verizon.net</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>215-842-2227</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Wynnewood Chiropractic</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>http://www.wynnewood-chiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>main@wynnewood-chiropractic.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>215-452-5382, 610-476-8795, +1-484-472-2134</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Intune Lifestyle</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://myintunelifestyle.com/</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>myintunelifestyle@gmail.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>267) 227-4743</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:12:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Torresdale Chiropractic Center</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>http://drcohenchiropractor.com/</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>drdave@drcohenchiropractor.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>215-333-6444</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:13:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Spinal Rehab Network</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>http://spinalrehabnetwork.com/</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>filler@godaddy.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>215-767-8218</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:13:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Redding Chiropractic</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://drcredding.com/</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>redding@drcredding.com, drzoey@drcredding.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>484-441-3064, 484-441-3186</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:13:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6808 Chiropractic Center</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>http://drcohenchiropractor.com/</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>drdave@drcohenchiropractor.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>215-333-6444</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:13:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>City Spine and Injury</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.cityspineandinjury.com/</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>cityspineandinjury@gmail.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>215-664-2229</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:14:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dr. Jeff Sklar, Chiropractor on the Hill</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>http://sklarchiro.com/</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>drjeff@sklarchiro.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>215) 498-5825</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:14:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Reboot Integrative Wellness Center-Chinatown</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>http://www.rebootiwc.com/</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>admin@rebootiwc.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>267-909-8877, 267-639-2336, 2157821614</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:14:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Renaissance Healing Arts</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>http://renaissancehealingarts.com/</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>info@renaissancehealingarts.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>215) 985-1344</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Main Line Disc | Chiropractor, Sciatica, Spinal Decompression</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://mainlinedisc.com/</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>info@mainlinedisc.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>610) 665-3953, 610) 853-8113, 610-665-3953</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dr. David Cohen</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>http://drcohenchiropractor.com/</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>drdave@drcohenchiropractor.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>215-333-6444</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Leads.xlsx
+++ b/Leads.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1604,6 +1604,2106 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>American HVAC Corp – Top HVAC Contractor NYC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://americanhvac.nyc/locations/manhattan-ny/</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>info@americanhvaccorp.com, info@americanhvaccorp.com​</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>347) 382-9030</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:45:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Top HVAC NYC</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://hvacairconditionersnyc.com/</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>support@hvacairconditionersnyc.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>646) 493-4904</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:45:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Figlia &amp; Sons Inc</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://figliasons.com/</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sales@figliasons.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>212-686-0094, 212-473-6409, 212.686.0094</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:45:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>212 HVAC Brooklyn</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>http://www.212hvac.com/</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>info@212hvac.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>212) 624-2505, 917) 633-5959</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:45:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FLOW HVAC NY | PTAC Installation &amp; Repair NYC</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://flowhvacnyc.com/</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>info@flowhvacnyc.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>212) 731-8383</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:45:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chelsea Cooling and Heating Services</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://chelseacoolingandheating.com/</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>service@chelseacoolingandheating.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>646-844-5455</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:45:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>24/7 HVAC LOCAL OF MANHATTAN NYC ELITH</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://247hvacnyc.com/</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>hvac6671@gmail.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>516) 717-7515</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:45:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>American HVAC Corp - Brooklyn, Heating, Air Conditioning, Refrigeration, Ductless Mini Split, Rooftop, Commercial HVAC NYC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://americanhvac.nyc/locations/brooklyn-ny/</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>info@americanhvaccorp.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>332) 232-9300</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:45:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MR. AIR NYC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>http://www.mrairnyc.com/</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>info@mrairnyc.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>212) 393-4822</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:45:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>American HVAC Corp - Queens, Ductless Mini Split Air Conditioner, VRF, Rooftop Units, Commercial HVAC Repair Installation NYC</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://americanhvac.nyc/locations/queens-ny/</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>info@americanhvaccorp.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>347) 862-9594</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:45:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>212 HVAC NYC</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://www.212hvac.com/</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>info@212hvac.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>212) 624-2505, 917) 633-5959</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:46:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kraus HVAC Repair</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://kraus-hvac-repair-s3u7gf1a.durable.site/</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>email@mybusiness.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>+1 929-325-2750</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:46:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Manhattan HVAC &amp; Appliance Repair Inc</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.manhattan-hvac-repair.com/</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>hvacr.repair.manhattan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>929) 381-0382</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:46:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>24/7 Manhattan Heating &amp; Air Conditioning</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://manhattan-hvac.com/</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>contact@manhattan-hvac.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>+1 646-503-0049, +1 6467 871 064</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:46:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Top Rated Local Hvac NYC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>http://topratedlocalhvac.com/</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>info@topratedlocalhvac.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>516) 834-4008</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:46:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Tribeca Airconditioning corp</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.tribecaair.com/</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>tribecaair@gmail.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>347) 202-4625, 914) 363-4420</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:46:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>HVAC SERVICE NYC</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>http://hvacservicenyc.com/</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>services@hvacservicenyc.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>718) 360-6030</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:46:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Interstate Air Conditioning &amp; Heating</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.interstateair.com/</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>info@interstateair.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>212-983-3330, 908-497-7793</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:46:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>New York HVAC NYC</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>http://newyorkhvacnyc.com/</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>services@hitechcentralair.com, ac@ptac.nyc</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>631) 500-2060</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:46:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>HVAC Specialist NYC</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>http://hvacspecialistnyc.com/</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>info@hvacspecialistnyc.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>631) 505-0035</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:46:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Neptune Air Conditioning</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.airconditioninginnyc.com/</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>info@neptuneac.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>646.863.2132</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:46:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>American HVAC Corp - Bronx - Heating, Commercial, Air Conditioning, Ductless Mini Split AC, Furnace Repair Installation NYC</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://americanhvac.nyc/locations/bronx-ny/</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>info@americanhvaccorp.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>929) 998-9370</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:46:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>City Cool Air Inc | Ptac Installation HVAC Repair NYC</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://citycoolair.com/</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>info@citycoolair.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>917) 325-1540</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:47:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Yan HVAC Refrigerator Appliances Repair</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://marcoyann2.wixsite.com/yanhvac/</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>yanhvac888@gmail.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>646) 331-5962</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:47:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Cozy Air Conditioning</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://cozyairconditioning.com/</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>chris@cozyairconditioning.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>212-971-1383, 212)683-9101</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:47:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>New York Best AC Repair Services.</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>http://www.newyorkbestacrepairservices.com/</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>info@newyorkbestacrepairservices.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>516) 834-4002</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:47:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Top HVAC NYC</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>http://www.tophvacnyc.com/</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>info@tophvacnyc.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>914) 401-0012</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:47:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>On Time HVAC</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://ontimehvacservices.com/</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>info@ontimehvacservices.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>646) 859-4378</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:47:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Super New York AC and Heating Repair</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://super-ny-hvac.com/</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>contact@super-ny-hvac.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>+1 646-692-0033, +1 6467 599 986</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:47:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>New York Heating Corporation</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>http://www.newyorkheating.com/?utm_source=GBP&amp;utm_medium=GBP&amp;utm_campaign=GBP</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>info@newyorkheating.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>718-963-2642, 718-782-3894</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:47:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Vital HVAC &amp; PTAC Solutions</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>http://www.vitalptacsolutions.com/</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>info@vitalptacsolutions.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>516) 854-6004</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:47:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Cool Air Inc Manhattan - HVAC Contractor | PTAC Services | AC Repair and Cleaning</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>http://coolairincmanhattan.com/</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>info@coolairincmanhattan.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>7187212131, 516) 309-0909, 718) 721-2131</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:48:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>New York Cooling Heating Services</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>http://coolingheatingnyc.com/</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>info@coolingheatingnyc.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>516) 517-0005</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:48:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>365 Kool</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>http://www.365kool.com/</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>365kool@gmail.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>347-821-0344</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:48:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>HVAC Repair</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://hvac-repair.net/</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>info@hvac-repair.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>646) 832-4279</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:48:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Platinum Heating &amp; Cooling</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://platinumhvac.us/</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>info@platinumhvac.us</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>908) 460-7420</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:48:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Weather Masters Nyc</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://weathermastersnyc.com/</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>info@weathermastersnyc.com, weathermastersnyc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>+1 (929) 260-8999</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:48:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jupiter HVAC Repairs NEW YORK</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>http://www.h2oairconditioning.com/</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>info@h2oairconditioning.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>212) 920-5009, 914) 740-8002</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:48:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Best HVAC Repair Service Company</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://thebesthvacrepair.com/</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>contact@besthvacrservice.com, contact@thebesthvacrepair.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>+1 6469 161 135</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:48:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>New York Hvac Choice</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://www.newyorkhvacchoice.com/</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>info@newyorkhvacchoice.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>212) 542-0411</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:48:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AIR CREW NYC INC.</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>http://www.aircrewnyc.com/</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>info@aircrewnyc.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>718) 790-8172</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:48:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Marvel HVAC Repairs NY</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://marvel-hvac.com/</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>contact@marvel-hvac.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>+1 6468 636 971</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:48:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Blue Star Air Conditioning NYC</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://bluestarairconditioningnyc.com/</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>info@bluestarairconditioningnyc.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>646 645-2835</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:49:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Riley's A/C and Heat</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://rileys-hvac.com/</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>contact@rileys-hvac.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>+1 929-298-9750, 929) 298-9750</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:49:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Pro Top HVAC Service</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://protophvac.com/</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>info@protophvac.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>646-601-6886, +1 646-601-6886</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:49:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>NewYork PTAC Services NYC.</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://ptacinny.com/</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>info@ptacinny.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>631) 602-0125</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:49:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>HVAC Service Experts NYC.</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>http://www.hvacserviceexpertsnyc.com/</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>info@hvacserviceexpertsnyc.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>551) 866-1004</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AIRCARE HVAC SERVICES NYC</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>http://www.aircarehvacnyc.com/</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>info@aircarehvacnyc.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>917) 540-2444</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:49:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>NewYork Hvac Solutions</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>http://newyorkhvacsolutions.com/</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>info@newyorkhvacsolutions.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>917) 341-0235</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:49:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>NYC Air Conditioning Professionals LLC</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://nycairpro.com/</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>contact@nycairpro.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>+1 9295 435 944</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2026-05-11 02:49:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Leads.xlsx
+++ b/Leads.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3704,6 +3704,296 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Skinova Medspa</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>http://www.skinovamedspa.com/</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>contact@skinovamedspa.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Medspa / Aesthetics</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026-05-21 02:52:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ZZ Med Spa</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://zzmedspa.com/</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>zzspabookings@gmail.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>917) 905-4928, +1 (917) 905-4928, +1 917-905-4928</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Medspa / Aesthetics</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026-05-21 02:53:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Revival Med Spa</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://revivalmedicalspa.com/</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>info@revivalmedicalspa.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>+1 929 383 2525</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Medspa / Aesthetics</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026-05-21 02:53:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BeautyFix Medspa Flatiron</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>http://www.beautyfixmedspa.com/</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>customerservice@beautyfixmedspa.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2123664787, 212) 366-4787</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Medspa / Aesthetics</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026-05-21 02:53:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SkinTight MedSpa</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://www.skintightmedspa.com/</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>info@skintightmedspa.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>212.452.1235, 212-452-1235</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Medspa / Aesthetics</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-05-21 02:53:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MiracleFace MedSpa</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://miraclefacemedspanyc.com/</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>info@miraclefacemedspanyc.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>212) 920-7790</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Medspa / Aesthetics</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026-05-21 02:53:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ZZ Med Spa</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://zzmedspa.com/</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>zzspabookings@gmail.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>917) 905-4928, +1 (917) 905-4928, +1 917-905-4928</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Medspa / Aesthetics</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-05-21 02:53:28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Leads.xlsx
+++ b/Leads.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3994,6 +3994,1468 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Warrior NYC</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>http://warrior.nyc/</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>info@warrior.nyc</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>646) 908-0923</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:59:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>UNITY Chiropractic Wellness</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>http://www.unitycw.com/</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>info@unitycw.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>347)685-1936, 917) 338-7811</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:59:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Oasis Chiropractic and Wellness Center</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://oasisfromthepain.com/</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>leslie@mindstorm.ca</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>212-582-1122, 212) 582-1122, 917) 210-3195</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:59:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>InSpine Health | NYC Chiropractor</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>http://www.inspinehealth.com/</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>info@inspinehealth.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>6467059234</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:00:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>I Know My Chiro, Chiropractic Wellness</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://iknowmychiro.com/?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=gbp</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>info@iknowmychiro.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>212-933-0188</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:00:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Specific Chiropractic</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://gonsteadnyc.com/</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>info@gonsteadnyc.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>10022 212-486, 212) 486-9800</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:00:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Active Health Chiropractic</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.activehealthchiropracticnyc.com/</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>info@ahc-nyc.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>917) 2617090, 917) 261-7090</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:00:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Dr. Watins - West Side Comprehensive Chiropractic</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://www.drwatins.com/?utm_source=google&amp;utm_medium=gmb_url&amp;utm_campaign=gmb_listing&amp;utm_content=primary</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>frontdesk@drwatins.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>212) 765-6470</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:01:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Lamb Chiropractic, Adam Lamb DC</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://topchiropractornyc.com/</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>lambchiro@gmail.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>+1.212.883.8700, 212.883.8700, 212) 883-8700</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:01:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Chelsea Chiropractic and Massage | NYC Chiropractor</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://chelseachiropracticandmassage.com/</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>info@chelseachiropracticandmassage.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>212-243-6384, 917-725-3373</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:01:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Level Up Sports Chiropractic - Dr. Daniel Huang D.C.</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>http://www.levelupsportschiro.com/</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>info@levelupsportschiro.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>646) 397-7109</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Upper East Side Chiropractic &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://www.ueschiro.com/</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>info@ueschiro.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>833-427-1080, 212-472-5558</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:01:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Energy Chiropractic</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>http://www.energychironyc.com/</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>info@energychironyc.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>212) 777-3301</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:01:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Healthy Choice Chiropractic - Dr. Sam Libenzon</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>http://www.healthychoicechiro.com/</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>info@healthychoicechiro.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>646) 996-4579</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Tribeca Family Chiropractic</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.tribecafamilychiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>drvirna@lampinstein.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>917-426-6751</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:02:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Encore Chiropractic</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>http://encorechiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>connect@encorechiropractic.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>646) 518-8696, 4126089387</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:02:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Dr Robert Morrison (NYC Chiropractor)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>http://www.robertmorrison.nyc/</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>dr@robertmorrison.nyc</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>646-389-9163</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:02:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Dr. Louis T. Calvano, chiropractor</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>http://www.calvanochiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>calvanochiropractic@gmail.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>212-369-5490</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:03:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Dr Monisha Mallik – Chiropractor Chelsea NYC</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.drmonishamallik.com/?utm_source=google&amp;utm_medium=googleplaces&amp;utm_campaign=drmonisha&amp;utm_id=GMB</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>hello@drmonishamallik.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>917-300-9702</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:03:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Atlant Chiropractic - Aleksander Kanevsky, DC</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://atlantchiropractic.com/chiropractic/</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>atlantchiro@gmail.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>212) 888-0520</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:03:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>The Wellness Center of NY</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://thewellnesscenterofny.com/</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>reception@thewellnesscenterofny.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>212.980.5444, 212)980-5444</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:03:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>34th Street Chiropractic and Wellness</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://www.healthcarechiropractic.com/?utm_source=gmb_auth</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>34thstreetwellness@gmail.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>212) 502-1804, 212-502-1803</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:03:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Cruz Chiropractic Wellness</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>http://cruzchirowellness.com/</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>info@cruzchirowellness.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:03:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Empire City Chiropractic</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://www.empirecitychiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>schedule@empirecitychiropractic.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:03:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Nachmias Chiropractic: Nachmias Adam L DC</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>http://www.calldradam.com/</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>calldradam@gmail.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>212.924.1700, 718.238.8900, 212-924-1700</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:04:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Warrior NYC Acupuncture</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>http://warrior.nyc/</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>info@warrior.nyc</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>646) 908-0923</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:04:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Mango Chiropractic, PC</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>http://mangochiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>mangochiropractic@gmail.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>917-338-6048</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:04:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Kang Corrective Chiropractic P.C.</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>http://kangchiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>info@kangchiropractic.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>212 779 2115</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:04:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Pain Care Chiropractic</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>http://www.paincarechiro.com/</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>paincarechiropractic@gmail.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>212-966-9899</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:04:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Back and Body Medical</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://backandbodyny.com/</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>your.friends@backandbodyny.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>212) 371-2000</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:04:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>B2B Chiropractor</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://www.b2bchiropractor.com/</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>info@b2bchiropractor.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>917-789-2216</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:04:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Cornerstone Chiropractic</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://cornerstonechiro.us/</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>standchiro@gmail.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>917.344.0158</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:05:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Heller Jay DC</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>http://www.jayhellerchiropractor.com/</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>backbones119@gmail.com, backbones@aol.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>917-620-1057, 212-243-6384</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:05:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>naderi chiropractic</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://www.naderichiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>info@naderichiropractic.com</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>646) 849-4232</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:05:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Fuel Sport &amp; Spine</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://fuelsportandspine.com/</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>admin@fuelsportandspine.com</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>646.478.8700</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-05-31 03:05:13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Leads.xlsx
+++ b/Leads.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5456,6 +5456,1510 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Warrior NYC</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>http://warrior.nyc/</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>info@warrior.nyc</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>646) 908-0923</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-07-01 02:59:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>UNITY Chiropractic Wellness</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>http://www.unitycw.com/</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>info@unitycw.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>347)685-1936, 917) 338-7811</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:00:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Oasis Chiropractic and Wellness Center</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://oasisfromthepain.com/</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>leslie@mindstorm.ca</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>212-582-1122, 917) 210-3195, 212) 582-1122</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>InSpine Health | NYC Chiropractor</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>http://www.inspinehealth.com/</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>info@inspinehealth.com</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>6467059234</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:00:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Specific Chiropractic</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://gonsteadnyc.com/</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>info@gonsteadnyc.com</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>10022 212-486, 212) 486-9800</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:00:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Liberty Wellness &amp; Chiropractic</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>http://www.libertychirofidi.com/?utm_campaign=gmb</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>info@libertychirofidi.com</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>212) 256-1171, 212.256.1171, 212-256-1171</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:01:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Pico Family Chiropractic Center</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://drpico.com/</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>drpico@drpico.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>212) 765-1333</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:01:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Dr. Watins - West Side Comprehensive Chiropractic</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://www.drwatins.com/?utm_source=google&amp;utm_medium=gmb_url&amp;utm_campaign=gmb_listing&amp;utm_content=primary</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>frontdesk@drwatins.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>212) 765-6470</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:01:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Stekel Chiropractic: Dani Stekel, D.C.</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>http://www.stekelchiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>drstekel@gmail.com, email@yoursite.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>212.581.3331, 212-581-3331</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:01:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Active Health Chiropractic</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://www.activehealthchiropracticnyc.com/</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>info@ahc-nyc.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>917) 261-7090, 917) 2617090</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Level Up Sports Chiropractic - Dr. Daniel Huang D.C.</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>http://www.levelupsportschiro.com/</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>info@levelupsportschiro.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>646) 397-7109</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:01:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Upper East Side Chiropractic &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://www.ueschiro.com/</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>info@ueschiro.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>212-472-5558, 833-427-1080</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:01:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Dr Monisha Mallik – Chiropractor Chelsea NYC</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://www.drmonishamallik.com/?utm_source=google&amp;utm_medium=googleplaces&amp;utm_campaign=drmonisha&amp;utm_id=GMB</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>hello@drmonishamallik.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>917-300-9702</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:01:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>I Know My Chiro, Chiropractic Wellness</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://iknowmychiro.com/?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=gbp</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>info@iknowmychiro.com</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>212-933-0188</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:02:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Alive &amp; Well Chiropractic</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>http://www.chiroalive.com/</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>chiroalive124@gmail.com</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>212) 661-7744, 212-661-7744</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Dr. Brian Blatt Chiropractic and Applied Kinesiology</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>http://www.drbrianblatt.com/</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>contact@drbrianblatt.com</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>212-633-0783</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:02:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Lamb Chiropractic, Adam Lamb DC</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://topchiropractornyc.com/</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>lambchiro@gmail.com</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>212) 883-8700, 212.883.8700, +1.212.883.8700</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:02:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Dr Robert Morrison (NYC Chiropractor)</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>http://www.robertmorrison.nyc/</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>dr@robertmorrison.nyc</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>646-389-9163</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:02:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Back and Body Medical</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>https://backandbodyny.com/</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>your.friends@backandbodyny.com</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>212) 371-2000</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Nachmias Chiropractic: Nachmias Adam L DC</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>http://www.calldradam.com/</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>calldradam@gmail.com</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>718.238.8900, 212.924.1700, 718-238-8900</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:02:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Dr. Louis T. Calvano, chiropractor</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>http://www.calvanochiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>calvanochiropractic@gmail.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>212-369-5490</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:02:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>B2B Chiropractor</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://www.b2bchiropractor.com/</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>info@b2bchiropractor.com</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>917-789-2216</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:03:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Tribeca Family Chiropractic</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://www.tribecafamilychiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>drvirna@lampinstein.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>917-426-6751</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:03:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>The Wellness Center of NY</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>https://thewellnesscenterofny.com/</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>reception@thewellnesscenterofny.com</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>212.980.5444, 212)980-5444</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:03:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Atlant Chiropractic - Aleksander Kanevsky, DC</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>https://atlantchiropractic.com/chiropractic/</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>atlantchiro@gmail.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>212) 888-0520</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:03:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Spine Atelier NYC</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://www.spineateliernyc.com/</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>admin@spineateliernyc.com, info@mysite.com</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>347) 292-9425</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:03:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Energy Chiropractic</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>http://www.energychironyc.com/</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>info@energychironyc.com</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>212) 777-3301</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:03:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Empire City Chiropractic</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>https://www.empirecitychiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>schedule@empirecitychiropractic.com</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:04:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>34th Street Chiropractic and Wellness</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>https://www.healthcarechiropractic.com/?utm_source=gmb_auth</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>34thstreetwellness@gmail.com</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>212-502-1803, 212) 502-1804</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:04:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Dr. Randi Jaffe</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>http://drrandijaffe.com/</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>drrandijaffe@gmail.com</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>10010 917-882</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:04:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Cruz Chiropractic Wellness</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>http://cruzchirowellness.com/</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>info@cruzchirowellness.com</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:04:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Heller Jay DC</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>http://www.jayhellerchiropractor.com/</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>backbones@aol.com, backbones119@gmail.com</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>917-620-1057, 212-243-6384</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Mango Chiropractic, PC</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>http://mangochiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>mangochiropractic@gmail.com</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>917-338-6048</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:04:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Kang Corrective Chiropractic P.C.</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>http://kangchiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>info@kangchiropractic.com</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>212 779 2115</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:05:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Verte Health</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://vertehealth.com/</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>info@vertehealth.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>888) 392-1218, 212) 328-9444</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:05:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Encore Chiropractic</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>http://encorechiropractic.com/</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>connect@encorechiropractic.com</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>4126089387, 646) 518-8696</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Chiropractors</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:05:16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
